--- a/исправления внести/слова2.xlsx
+++ b/исправления внести/слова2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD249F3-209B-4C8B-BD2C-0DFB3B7DE33C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9112AA5-E376-45D1-9D15-72D2423FE678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="cоставные" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>биологический структурализм</t>
   </si>
@@ -48,41 +48,6 @@
     <t>прямых излучений</t>
   </si>
   <si>
-    <t>кто в этом случая</t>
-  </si>
-  <si>
-    <t>кто в этом случае</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>релятивисткая</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> теория гравитации</t>
-    </r>
-  </si>
-  <si>
-    <t>представление об энергоинформационной устройстве человека</t>
-  </si>
-  <si>
-    <t>представление об энергоинформационном устройстве человека</t>
-  </si>
-  <si>
     <t>возможны два исхода его возврата</t>
   </si>
   <si>
@@ -92,18 +57,6 @@
     <t>контактантов</t>
   </si>
   <si>
-    <t>последователи этого обособленного закрытого вероучения</t>
-  </si>
-  <si>
-    <t>последователи этой обособленные закрытые вероучения</t>
-  </si>
-  <si>
-    <t>общего научного савокупности миропонимания</t>
-  </si>
-  <si>
-    <t>общей научной савокупности миропонимания</t>
-  </si>
-  <si>
     <t>запасенный жизненный щаряд вращение скрученного</t>
   </si>
   <si>
@@ -134,30 +87,12 @@
     <t>Животным это используется в брачных танцах</t>
   </si>
   <si>
-    <t>Мыслящего Океана покрывавшего небесому телу</t>
-  </si>
-  <si>
-    <t>Мыслящего Океана покрывавшего небесое тело</t>
-  </si>
-  <si>
     <t>Вода является двухмерной отображением рычага</t>
   </si>
   <si>
     <t>Вода является двухмерным отображением рычага</t>
   </si>
   <si>
-    <t>наступают связующие случая</t>
-  </si>
-  <si>
-    <t>наступают связующие случаи</t>
-  </si>
-  <si>
-    <t>сведения может быть записана</t>
-  </si>
-  <si>
-    <t>сведения могут быть записаны</t>
-  </si>
-  <si>
     <t>молекулярное устройство углерода</t>
   </si>
   <si>
@@ -170,48 +105,6 @@
     <t>как "считываются" сведения</t>
   </si>
   <si>
-    <t>очередная обьединение общества</t>
-  </si>
-  <si>
-    <t>очередное обьединение общества</t>
-  </si>
-  <si>
-    <t>по воле чуждого земной развития злого разума</t>
-  </si>
-  <si>
-    <t>по воле чуждому земному развитию злого разума</t>
-  </si>
-  <si>
-    <t>последствие известен давно</t>
-  </si>
-  <si>
-    <t>последствие известно давно</t>
-  </si>
-  <si>
-    <t>На первый взгляд жуткий истребление народа</t>
-  </si>
-  <si>
-    <t>На первый взгляд жуткое истребление народа</t>
-  </si>
-  <si>
-    <t>по 10 сложилась случай воплощения</t>
-  </si>
-  <si>
-    <t>по 10 сложился случай воплощения</t>
-  </si>
-  <si>
-    <t>один из парламентариев в беседа</t>
-  </si>
-  <si>
-    <t>один из парламентариев в беседе</t>
-  </si>
-  <si>
-    <t>после любой даже незначительный увечья</t>
-  </si>
-  <si>
-    <t>после любого даже незначительного увечья</t>
-  </si>
-  <si>
     <t>внедрение энергоинформационного зараза</t>
   </si>
   <si>
@@ -224,112 +117,34 @@
     <t>и эта зараза дала намеченые плоды</t>
   </si>
   <si>
-    <t>паталогия в развития землян</t>
-  </si>
-  <si>
-    <t>паталогия в развитии землян</t>
-  </si>
-  <si>
-    <t>протекающий по завитка</t>
-  </si>
-  <si>
-    <t>протекающий по завиткам</t>
-  </si>
-  <si>
-    <t>наше небесное тело было превращено в некое жертвенное посевное поле</t>
-  </si>
-  <si>
-    <t>наше небесное тело была превращена в некую жертвенную посевное поле</t>
-  </si>
-  <si>
     <t>любые сведения из Несущих сведения Полей должна восприниматься</t>
   </si>
   <si>
     <t>любые сведения из Несущих сведений Полей должны восприниматься</t>
   </si>
   <si>
-    <t>неизбежно часть сведениям теряется</t>
-  </si>
-  <si>
-    <t>неизбежно часть сведениий теряется</t>
-  </si>
-  <si>
-    <t>об энергоинформационной устройстве человека</t>
-  </si>
-  <si>
-    <t>об энергоинформационном устройстве человека</t>
-  </si>
-  <si>
     <t>При этом образуется количественная устройство напоминающая</t>
   </si>
   <si>
     <t>При этом образуется количественное  устройство напоминаящее</t>
   </si>
   <si>
-    <t>наша существующая живая особь</t>
-  </si>
-  <si>
-    <t>наш существующий живая особь</t>
-  </si>
-  <si>
-    <t>происходит  разрушение внутренней устройства</t>
-  </si>
-  <si>
-    <t>происходит  разрушение внутреннего устройства</t>
-  </si>
-  <si>
-    <t>ожидает весьма неприятная случай</t>
-  </si>
-  <si>
-    <t>ожидает весьма неприятный случай</t>
-  </si>
-  <si>
     <t>выполлняют основную значение</t>
   </si>
   <si>
     <t>выполлняют основное значение</t>
   </si>
   <si>
-    <t>нуждаются в притоке нового возможности</t>
-  </si>
-  <si>
-    <t>нуждаются в притоке новоой возможности</t>
-  </si>
-  <si>
-    <t>политичекий и экономический возможность</t>
-  </si>
-  <si>
-    <t>политичекую и экономическую возможность</t>
-  </si>
-  <si>
     <t>есть какая то щелчка, действующая на погибель</t>
   </si>
   <si>
     <t>есть какой то щелчок, действующий на погибель</t>
   </si>
   <si>
-    <t>нельзя было дать российскому народу</t>
-  </si>
-  <si>
-    <t>нельзя было дать российскому народности</t>
-  </si>
-  <si>
-    <t>нужна и непосредственная обряд</t>
-  </si>
-  <si>
-    <t>нужнен и непосредственный обряд</t>
-  </si>
-  <si>
     <t>два года назад могла за считанные минуты пройти</t>
   </si>
   <si>
     <t>два года назад могло за считанные минуты пройти</t>
-  </si>
-  <si>
-    <t>обнаружили сильнейший напряжение</t>
-  </si>
-  <si>
-    <t>обнаружили сильнейшее напряжение</t>
   </si>
   <si>
     <t>время изменения позволил выявить следующее</t>
@@ -372,7 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,20 +202,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -452,13 +253,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -793,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
-  <dimension ref="A5:B72"/>
+  <dimension ref="A5:B33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.81640625" customWidth="1"/>
@@ -807,415 +607,195 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
+      <c r="A11" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" t="s">
-        <v>26</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" t="s">
-        <v>44</v>
+      <c r="A32" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>84</v>
-      </c>
-      <c r="B37" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>85</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>89</v>
-      </c>
-      <c r="B41" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>79</v>
-      </c>
-      <c r="B49" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="B33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B52" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>67</v>
-      </c>
-      <c r="B54" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>71</v>
-      </c>
-      <c r="B55" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>95</v>
-      </c>
-      <c r="B59" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>31</v>
-      </c>
-      <c r="B60" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B103">
-    <sortCondition ref="A2:A103"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B64">
+    <sortCondition ref="A2:A64"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -1232,7 +812,7 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/слова2.xlsx
+++ b/исправления внести/слова2.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9112AA5-E376-45D1-9D15-72D2423FE678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33951B56-4C24-49D9-AF2F-180BE39066C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-19305" yWindow="3330" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="cоставные" sheetId="2" r:id="rId1"/>
-    <sheet name="автору отправить" sheetId="3" r:id="rId2"/>
+    <sheet name="одичночные" sheetId="4" r:id="rId2"/>
+    <sheet name="автору отправить" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">одичночные!$A$1:$B$277</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32,12 +36,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="372">
   <si>
     <t>биологический структурализм</t>
   </si>
@@ -181,13 +188,985 @@
   </si>
   <si>
     <t>выглядел ход энергоинформационного изменения</t>
+  </si>
+  <si>
+    <t>исходные</t>
+  </si>
+  <si>
+    <t>перевод</t>
+  </si>
+  <si>
+    <t>энергоинформационный</t>
+  </si>
+  <si>
+    <t>фаллос</t>
+  </si>
+  <si>
+    <t>энвальтирование</t>
+  </si>
+  <si>
+    <t>эгрэгор</t>
+  </si>
+  <si>
+    <t>эксирополяция</t>
+  </si>
+  <si>
+    <t>микролептонных</t>
+  </si>
+  <si>
+    <t>тахионных</t>
+  </si>
+  <si>
+    <t>животно</t>
+  </si>
+  <si>
+    <t>животное</t>
+  </si>
+  <si>
+    <t>командировку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">аквариумист </t>
+  </si>
+  <si>
+    <t>станции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Морфогенным </t>
+  </si>
+  <si>
+    <t xml:space="preserve">кодировку </t>
+  </si>
+  <si>
+    <t>тримеров, тетрамеров, пентамеров и гексамеров</t>
+  </si>
+  <si>
+    <t>органов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">энергетической </t>
+  </si>
+  <si>
+    <t xml:space="preserve">жестикулирующий </t>
+  </si>
+  <si>
+    <t>биоэнергетик</t>
+  </si>
+  <si>
+    <t>кампании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">антимиры </t>
+  </si>
+  <si>
+    <t>робот</t>
+  </si>
+  <si>
+    <t xml:space="preserve">космологический </t>
+  </si>
+  <si>
+    <t xml:space="preserve">иммунную </t>
+  </si>
+  <si>
+    <t xml:space="preserve">голографическую </t>
+  </si>
+  <si>
+    <t xml:space="preserve">метакодом </t>
+  </si>
+  <si>
+    <t xml:space="preserve">инвалидов </t>
+  </si>
+  <si>
+    <t xml:space="preserve">биополевой </t>
+  </si>
+  <si>
+    <t xml:space="preserve">кодированная </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Биоэнергетические </t>
+  </si>
+  <si>
+    <t>нуклиды</t>
+  </si>
+  <si>
+    <t>радикалы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">неперсонификации </t>
+  </si>
+  <si>
+    <t xml:space="preserve">нуклон </t>
+  </si>
+  <si>
+    <t>частица являющаяся основным составляющим атомного ядра</t>
+  </si>
+  <si>
+    <t>синапсов</t>
+  </si>
+  <si>
+    <t>место еонтактк между двумя нейронами</t>
+  </si>
+  <si>
+    <t xml:space="preserve">биолокационными </t>
+  </si>
+  <si>
+    <t>способность живых  организмов ориентироваться в прстранстве</t>
+  </si>
+  <si>
+    <t>энергетики</t>
+  </si>
+  <si>
+    <t>аура</t>
+  </si>
+  <si>
+    <t>невидимая оболочка вокруг живых существ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">экологическая </t>
+  </si>
+  <si>
+    <t xml:space="preserve">неоткорректированных </t>
+  </si>
+  <si>
+    <t>неисправленные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ультрафиолетового </t>
+  </si>
+  <si>
+    <t>невидимое человеческому глазу электроиагнитное излучение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">инфракрасного </t>
+  </si>
+  <si>
+    <t>тип лучистой энергии невидимый для глаза</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Хромосомы </t>
+  </si>
+  <si>
+    <t>стрруктурный элемент клеточного ядра содержащая опрелененный набор генов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ультразвука </t>
+  </si>
+  <si>
+    <t>звуковые волны неслышимые для человека</t>
+  </si>
+  <si>
+    <t xml:space="preserve">натальную </t>
+  </si>
+  <si>
+    <t>ваш индивидуаьный гороскоп рождения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">мембраны </t>
+  </si>
+  <si>
+    <t>тонкая пленка обладающая избирательной проницаемостью</t>
+  </si>
+  <si>
+    <t xml:space="preserve">романа </t>
+  </si>
+  <si>
+    <t>энвольтировать</t>
+  </si>
+  <si>
+    <t>изготовление куклы  образа человека с использованием его фотографий</t>
+  </si>
+  <si>
+    <t>панспермии</t>
+  </si>
+  <si>
+    <t>смесь всяких семян</t>
+  </si>
+  <si>
+    <t>сериалу</t>
+  </si>
+  <si>
+    <t>телебоевиков</t>
+  </si>
+  <si>
+    <t>жанр фильма или телесериала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">агентство </t>
+  </si>
+  <si>
+    <t>компания организация</t>
+  </si>
+  <si>
+    <t>аквариуме</t>
+  </si>
+  <si>
+    <t>прозрачный сосуд для рыб</t>
+  </si>
+  <si>
+    <t>любитель аквариумов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">алкогольных </t>
+  </si>
+  <si>
+    <t>хмельной спиртной</t>
+  </si>
+  <si>
+    <t>аминокислот</t>
+  </si>
+  <si>
+    <t>лорганические соединения белков</t>
+  </si>
+  <si>
+    <t>ангины</t>
+  </si>
+  <si>
+    <t>инфекционное заболевание миндалин</t>
+  </si>
+  <si>
+    <t xml:space="preserve">астрофизические </t>
+  </si>
+  <si>
+    <t>звездный космический небесный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">атеросклеротические </t>
+  </si>
+  <si>
+    <t>хроническое заболевание артерий</t>
+  </si>
+  <si>
+    <t>атлас</t>
+  </si>
+  <si>
+    <t>книга альбом карта</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> свечение атмосфера биополе</t>
+  </si>
+  <si>
+    <t>бактерий</t>
+  </si>
+  <si>
+    <t>микроб микроорганизм</t>
+  </si>
+  <si>
+    <t>способность живых сущуств ощущать скрытые объекты</t>
+  </si>
+  <si>
+    <t>жизненное поле</t>
+  </si>
+  <si>
+    <t>целитель</t>
+  </si>
+  <si>
+    <t>целительные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">борону </t>
+  </si>
+  <si>
+    <t>грабли плоскорез</t>
+  </si>
+  <si>
+    <t>браконьером</t>
+  </si>
+  <si>
+    <t>нарушитель охотничьих правил</t>
+  </si>
+  <si>
+    <t>бронхиты</t>
+  </si>
+  <si>
+    <t>воспаление бронхов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">варикозному </t>
+  </si>
+  <si>
+    <t>расширение вен нижних конечностей</t>
+  </si>
+  <si>
+    <t>внутрипарный</t>
+  </si>
+  <si>
+    <t>внутригрупповой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">высокоэнергетичных </t>
+  </si>
+  <si>
+    <t>высокозатратных</t>
+  </si>
+  <si>
+    <t>гарнитурой</t>
+  </si>
+  <si>
+    <t>комплект наушников комплект набор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гемаралитических </t>
+  </si>
+  <si>
+    <t>разрушуние эритрицитов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">геоцентрической </t>
+  </si>
+  <si>
+    <t>центрированный на Земле</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гильотина </t>
+  </si>
+  <si>
+    <t>ножницы эшафот резак</t>
+  </si>
+  <si>
+    <t>глюонного</t>
+  </si>
+  <si>
+    <t>безмассовая частица</t>
+  </si>
+  <si>
+    <t>голографии</t>
+  </si>
+  <si>
+    <t>обьемная фотография</t>
+  </si>
+  <si>
+    <t>государством</t>
+  </si>
+  <si>
+    <t>страна федерация власть республика правительство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гримасой </t>
+  </si>
+  <si>
+    <t>выражение лица кривляние</t>
+  </si>
+  <si>
+    <t xml:space="preserve">губернатор </t>
+  </si>
+  <si>
+    <t>глава администрации глава региона вождь начальник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">декламированием </t>
+  </si>
+  <si>
+    <t>чтение произнесение</t>
+  </si>
+  <si>
+    <t>дескать</t>
+  </si>
+  <si>
+    <t>мол якобы значит</t>
+  </si>
+  <si>
+    <t>деспотизмов</t>
+  </si>
+  <si>
+    <t>властность  насилие тирания деспотичность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">децетратной </t>
+  </si>
+  <si>
+    <t>кровь от  трупа</t>
+  </si>
+  <si>
+    <t>диване</t>
+  </si>
+  <si>
+    <t>кровать постель кушетка софа</t>
+  </si>
+  <si>
+    <t>домогательства</t>
+  </si>
+  <si>
+    <t>насилие притязания оскорбление прниставание</t>
+  </si>
+  <si>
+    <t>жернова</t>
+  </si>
+  <si>
+    <t>круг мельница</t>
+  </si>
+  <si>
+    <t>махающий руками</t>
+  </si>
+  <si>
+    <t>низкий грубый</t>
+  </si>
+  <si>
+    <t xml:space="preserve">запараллелено </t>
+  </si>
+  <si>
+    <t>уравнено согласовано составлено</t>
+  </si>
+  <si>
+    <t>икон</t>
+  </si>
+  <si>
+    <t>лицо образ изображение</t>
+  </si>
+  <si>
+    <t>защитную</t>
+  </si>
+  <si>
+    <t>калека  убогий</t>
+  </si>
+  <si>
+    <t>инквизиция</t>
+  </si>
+  <si>
+    <t>пытка мучение терзание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">интернационалист </t>
+  </si>
+  <si>
+    <t>мирожитель гражданин мира</t>
+  </si>
+  <si>
+    <t>тепловой термический</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ионизированных </t>
+  </si>
+  <si>
+    <t>осеребреный</t>
+  </si>
+  <si>
+    <t>кадилом</t>
+  </si>
+  <si>
+    <t>сосуд богородское  зелье</t>
+  </si>
+  <si>
+    <t>период война  деятельность работа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кандидатский </t>
+  </si>
+  <si>
+    <t>ученый докторский научный</t>
+  </si>
+  <si>
+    <t>зашифрованная закодированная</t>
+  </si>
+  <si>
+    <t>вахта поездка поручение</t>
+  </si>
+  <si>
+    <t>кондиции</t>
+  </si>
+  <si>
+    <t>тонус условия состояние</t>
+  </si>
+  <si>
+    <t>звездный небесный мировой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кристаллизации </t>
+  </si>
+  <si>
+    <t>затвердевание  отвердевание</t>
+  </si>
+  <si>
+    <t>ламинат</t>
+  </si>
+  <si>
+    <t>искуственный паркет</t>
+  </si>
+  <si>
+    <t>лигатурами</t>
+  </si>
+  <si>
+    <t>сязки букв</t>
+  </si>
+  <si>
+    <t>мамаи</t>
+  </si>
+  <si>
+    <t>богатырь воевода воин</t>
+  </si>
+  <si>
+    <t>перепонка покров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">менталитете </t>
+  </si>
+  <si>
+    <t>ум мышление мировозрение</t>
+  </si>
+  <si>
+    <t>система знаков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">метеоритной </t>
+  </si>
+  <si>
+    <t>падающей звездной космичечкой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мишенями </t>
+  </si>
+  <si>
+    <t>цель объект щит</t>
+  </si>
+  <si>
+    <t>формирующий структурный</t>
+  </si>
+  <si>
+    <t>мыльных опер»</t>
+  </si>
+  <si>
+    <t>мелодрамы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нейролингвистического </t>
+  </si>
+  <si>
+    <t>нейроязыковый</t>
+  </si>
+  <si>
+    <t>неисправленых необработанных</t>
+  </si>
+  <si>
+    <t>обезличивание обобщение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">низкоэнергетические </t>
+  </si>
+  <si>
+    <t>экономичные энергосберегающие</t>
+  </si>
+  <si>
+    <t>излтопы радионуклиды</t>
+  </si>
+  <si>
+    <t>ядерная частица</t>
+  </si>
+  <si>
+    <t xml:space="preserve">одномандатные </t>
+  </si>
+  <si>
+    <t>одноместные персональные уникальные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">окроплял </t>
+  </si>
+  <si>
+    <t>брызгал проливал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">онанизму </t>
+  </si>
+  <si>
+    <t>ручная рабрта самостимуляция</t>
+  </si>
+  <si>
+    <t>опер</t>
+  </si>
+  <si>
+    <t>язык театр искусство</t>
+  </si>
+  <si>
+    <t>оптики</t>
+  </si>
+  <si>
+    <t>линзы бинокли  лупы</t>
+  </si>
+  <si>
+    <t>часть тело система</t>
+  </si>
+  <si>
+    <t>оргиями</t>
+  </si>
+  <si>
+    <t>развраи гулянка</t>
+  </si>
+  <si>
+    <t>орденоносец</t>
+  </si>
+  <si>
+    <t>награжденный отличник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Орнитологи </t>
+  </si>
+  <si>
+    <t>птицеведы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">остеохондрозу </t>
+  </si>
+  <si>
+    <t>эрозия межпозвонковых дисков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">отреагировавшие </t>
+  </si>
+  <si>
+    <t>откликнувшиеся отозвавшиеся</t>
+  </si>
+  <si>
+    <t>оформлением</t>
+  </si>
+  <si>
+    <t>документ  удостоверение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">офтальмологической </t>
+  </si>
+  <si>
+    <t>глазной зрительный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ошеломил </t>
+  </si>
+  <si>
+    <t>поразил ошеломил потряс</t>
+  </si>
+  <si>
+    <t>внеземное зарождение жизни</t>
+  </si>
+  <si>
+    <t>пантаклями</t>
+  </si>
+  <si>
+    <t>знаки обереги талисманы</t>
+  </si>
+  <si>
+    <t>парафинируют</t>
+  </si>
+  <si>
+    <t>наносят парафин  обрабатывают парафином</t>
+  </si>
+  <si>
+    <t xml:space="preserve">партийном </t>
+  </si>
+  <si>
+    <t>партийного направления</t>
+  </si>
+  <si>
+    <t xml:space="preserve">паталогоанатомического </t>
+  </si>
+  <si>
+    <t>изучение болезней после смерти</t>
+  </si>
+  <si>
+    <t>персоналку</t>
+  </si>
+  <si>
+    <t>личный чат личная переписка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">пиелонефритом </t>
+  </si>
+  <si>
+    <t>воспаление почек</t>
+  </si>
+  <si>
+    <t>пласты</t>
+  </si>
+  <si>
+    <t>слои уровни полосы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">погонах </t>
+  </si>
+  <si>
+    <t>петлицы нашивки знаки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">полимолекулярных </t>
+  </si>
+  <si>
+    <t>полимерных многомолекулярных</t>
+  </si>
+  <si>
+    <t xml:space="preserve">полусекстиля </t>
+  </si>
+  <si>
+    <t>астрологический угол астрологическая связь</t>
+  </si>
+  <si>
+    <t>пост</t>
+  </si>
+  <si>
+    <t>часовой охранник</t>
+  </si>
+  <si>
+    <t>проформы</t>
+  </si>
+  <si>
+    <t>церемония показуха шаблон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">психолингвистики </t>
+  </si>
+  <si>
+    <t>психология языка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">психологизмом </t>
+  </si>
+  <si>
+    <t>психоанализ</t>
+  </si>
+  <si>
+    <t>психология</t>
+  </si>
+  <si>
+    <t>психика душевность</t>
+  </si>
+  <si>
+    <t>экстремисты бунтари новаторы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">расфасовываются </t>
+  </si>
+  <si>
+    <t>пакуются фасуются сортируются</t>
+  </si>
+  <si>
+    <t>режим</t>
+  </si>
+  <si>
+    <t>риртуал обряд обычай</t>
+  </si>
+  <si>
+    <t>механизм аппарат устройство</t>
+  </si>
+  <si>
+    <t>проза белетристика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сальтаницизма </t>
+  </si>
+  <si>
+    <t>ерунда чушь  глупость</t>
+  </si>
+  <si>
+    <t>светофоре</t>
+  </si>
+  <si>
+    <t>регулировщик</t>
+  </si>
+  <si>
+    <t>секс</t>
+  </si>
+  <si>
+    <t>близость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сексолог </t>
+  </si>
+  <si>
+    <t>консультант по сексуальной жизни</t>
+  </si>
+  <si>
+    <t>сексуальной энергии</t>
+  </si>
+  <si>
+    <t>половая энергия</t>
+  </si>
+  <si>
+    <t>многочасовой фильм</t>
+  </si>
+  <si>
+    <t>связь соединение</t>
+  </si>
+  <si>
+    <t>сканирование</t>
+  </si>
+  <si>
+    <t>цифровое копирование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">спеццентрала </t>
+  </si>
+  <si>
+    <t>спеццентр</t>
+  </si>
+  <si>
+    <t>вокзал терминал транспортный узел</t>
+  </si>
+  <si>
+    <t>субкультуры</t>
+  </si>
+  <si>
+    <t>молодежные движения  молодежные стили</t>
+  </si>
+  <si>
+    <t xml:space="preserve">суррогатной </t>
+  </si>
+  <si>
+    <t>заместительной поддельной ненастоящей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сутенеров </t>
+  </si>
+  <si>
+    <t>альфонс жигало растовщик</t>
+  </si>
+  <si>
+    <t>сверхсветовых</t>
+  </si>
+  <si>
+    <t>боевик на экране</t>
+  </si>
+  <si>
+    <t xml:space="preserve">техническом </t>
+  </si>
+  <si>
+    <t>технологический аппаратный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">техногенной </t>
+  </si>
+  <si>
+    <t>искуственный технологический</t>
+  </si>
+  <si>
+    <t>тордионов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">тримеров, тетрамеров, пентамеров </t>
+  </si>
+  <si>
+    <t>олигомеры полимеры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">тромбоцитов </t>
+  </si>
+  <si>
+    <t>кровяные клетки</t>
+  </si>
+  <si>
+    <t>звуковые волны неслышимые человеком</t>
+  </si>
+  <si>
+    <t>невидимый</t>
+  </si>
+  <si>
+    <t>факультета</t>
+  </si>
+  <si>
+    <t>институт курс академия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">фибраналитической </t>
+  </si>
+  <si>
+    <t>фильм</t>
+  </si>
+  <si>
+    <t>кинопоказ</t>
+  </si>
+  <si>
+    <t>фотомоделей</t>
+  </si>
+  <si>
+    <t>манекенщицы модели</t>
+  </si>
+  <si>
+    <t>хирургии</t>
+  </si>
+  <si>
+    <t>оперирование</t>
+  </si>
+  <si>
+    <t>генные носители</t>
+  </si>
+  <si>
+    <t xml:space="preserve">хулиганов </t>
+  </si>
+  <si>
+    <t>буйный задира баловник</t>
+  </si>
+  <si>
+    <t>шантажа</t>
+  </si>
+  <si>
+    <t>давление угроза запугивание</t>
+  </si>
+  <si>
+    <t>натуральная природная органическая</t>
+  </si>
+  <si>
+    <t>оценка предсказание прогнозирование</t>
+  </si>
+  <si>
+    <t>кукольная магия</t>
+  </si>
+  <si>
+    <t>окутывать обертывать</t>
+  </si>
+  <si>
+    <t>мощность сила активность</t>
+  </si>
+  <si>
+    <t>силовой активной динамичной</t>
+  </si>
+  <si>
+    <t>вибрационный  энергетический</t>
+  </si>
+  <si>
+    <t>энергопотенциала</t>
+  </si>
+  <si>
+    <t>энергетический ресурс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">энергоцентр </t>
+  </si>
+  <si>
+    <t>энергоблок электростанция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">эритроцитов </t>
+  </si>
+  <si>
+    <t>красные клетки крови</t>
+  </si>
+  <si>
+    <t xml:space="preserve">этилового </t>
+  </si>
+  <si>
+    <t>винный</t>
+  </si>
+  <si>
+    <t>обеликс</t>
+  </si>
+  <si>
+    <t>монумент</t>
+  </si>
+  <si>
+    <t>статуя памятник</t>
+  </si>
+  <si>
+    <t>сервисах</t>
+  </si>
+  <si>
+    <t>услугах системах приложениях</t>
+  </si>
+  <si>
+    <t>кроссворд</t>
+  </si>
+  <si>
+    <t>ребус задача игра</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +1198,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="LiberEmb"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -253,12 +1245,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -594,18 +1591,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
   <dimension ref="A5:B33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="48.81640625" customWidth="1"/>
-    <col min="2" max="2" width="67.26953125" customWidth="1"/>
+    <col min="1" max="1" width="48.84375" customWidth="1"/>
+    <col min="2" max="2" width="67.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -613,7 +1610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -621,7 +1618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -629,7 +1626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -637,7 +1634,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -645,7 +1642,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -653,7 +1650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -661,7 +1658,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -669,7 +1666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -677,7 +1674,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -685,7 +1682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -693,7 +1690,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -701,7 +1698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -709,7 +1706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -717,7 +1714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -725,7 +1722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -733,7 +1730,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -741,7 +1738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -749,11 +1746,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -761,7 +1758,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -769,7 +1766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" s="3" customFormat="1">
       <c r="A31" s="3" t="s">
         <v>28</v>
       </c>
@@ -777,7 +1774,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2">
       <c r="A32" s="4" t="s">
         <v>1</v>
       </c>
@@ -785,7 +1782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -803,14 +1800,1415 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4422D7C9-8DA6-4D05-8090-0A60A1B77BA5}">
+  <dimension ref="A1:B270"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="28.23046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>167</v>
+      </c>
+      <c r="B35" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>169</v>
+      </c>
+      <c r="B36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>171</v>
+      </c>
+      <c r="B37" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>173</v>
+      </c>
+      <c r="B38" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>177</v>
+      </c>
+      <c r="B40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>196</v>
+      </c>
+      <c r="B57" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>201</v>
+      </c>
+      <c r="B60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>208</v>
+      </c>
+      <c r="B66" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>370</v>
+      </c>
+      <c r="B67" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>210</v>
+      </c>
+      <c r="B68" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>212</v>
+      </c>
+      <c r="B69" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>214</v>
+      </c>
+      <c r="B70" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>105</v>
+      </c>
+      <c r="B71" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>105</v>
+      </c>
+      <c r="B72" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>217</v>
+      </c>
+      <c r="B73" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>222</v>
+      </c>
+      <c r="B77" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>366</v>
+      </c>
+      <c r="B78" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>103</v>
+      </c>
+      <c r="B81" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>227</v>
+      </c>
+      <c r="B82" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>82</v>
+      </c>
+      <c r="B85" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>231</v>
+      </c>
+      <c r="B86" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>80</v>
+      </c>
+      <c r="B87" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>83</v>
+      </c>
+      <c r="B88" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>83</v>
+      </c>
+      <c r="B89" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>235</v>
+      </c>
+      <c r="B91" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>237</v>
+      </c>
+      <c r="B92" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>239</v>
+      </c>
+      <c r="B93" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B94" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>243</v>
+      </c>
+      <c r="B95" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>65</v>
+      </c>
+      <c r="B96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>246</v>
+      </c>
+      <c r="B97" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>248</v>
+      </c>
+      <c r="B98" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>250</v>
+      </c>
+      <c r="B99" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>252</v>
+      </c>
+      <c r="B100" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>254</v>
+      </c>
+      <c r="B101" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>256</v>
+      </c>
+      <c r="B102" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>258</v>
+      </c>
+      <c r="B103" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>260</v>
+      </c>
+      <c r="B104" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>110</v>
+      </c>
+      <c r="B106" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>263</v>
+      </c>
+      <c r="B107" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>265</v>
+      </c>
+      <c r="B108" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>267</v>
+      </c>
+      <c r="B109" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>269</v>
+      </c>
+      <c r="B110" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>271</v>
+      </c>
+      <c r="B111" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>273</v>
+      </c>
+      <c r="B112" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>275</v>
+      </c>
+      <c r="B113" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>277</v>
+      </c>
+      <c r="B114" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>279</v>
+      </c>
+      <c r="B115" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>281</v>
+      </c>
+      <c r="B116" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>283</v>
+      </c>
+      <c r="B117" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>285</v>
+      </c>
+      <c r="B118" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>287</v>
+      </c>
+      <c r="B119" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>289</v>
+      </c>
+      <c r="B120" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>291</v>
+      </c>
+      <c r="B121" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>81</v>
+      </c>
+      <c r="B122" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>294</v>
+      </c>
+      <c r="B123" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>296</v>
+      </c>
+      <c r="B124" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>71</v>
+      </c>
+      <c r="B125" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>107</v>
+      </c>
+      <c r="B126" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>300</v>
+      </c>
+      <c r="B127" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>302</v>
+      </c>
+      <c r="B128" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>304</v>
+      </c>
+      <c r="B129" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>306</v>
+      </c>
+      <c r="B130" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>308</v>
+      </c>
+      <c r="B131" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>368</v>
+      </c>
+      <c r="B132" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>112</v>
+      </c>
+      <c r="B133" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>85</v>
+      </c>
+      <c r="B134" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>85</v>
+      </c>
+      <c r="B135" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>312</v>
+      </c>
+      <c r="B136" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>314</v>
+      </c>
+      <c r="B137" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>61</v>
+      </c>
+      <c r="B138" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>317</v>
+      </c>
+      <c r="B139" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>319</v>
+      </c>
+      <c r="B140" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>321</v>
+      </c>
+      <c r="B141" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>56</v>
+      </c>
+      <c r="B142" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>113</v>
+      </c>
+      <c r="B143" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>113</v>
+      </c>
+      <c r="B144" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>325</v>
+      </c>
+      <c r="B145" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>327</v>
+      </c>
+      <c r="B146" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>330</v>
+      </c>
+      <c r="B148" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>332</v>
+      </c>
+      <c r="B150" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>101</v>
+      </c>
+      <c r="B151" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>101</v>
+      </c>
+      <c r="B152" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>95</v>
+      </c>
+      <c r="B153" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>95</v>
+      </c>
+      <c r="B154" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>336</v>
+      </c>
+      <c r="B155" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>339</v>
+      </c>
+      <c r="B158" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>341</v>
+      </c>
+      <c r="B159" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>343</v>
+      </c>
+      <c r="B160" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>99</v>
+      </c>
+      <c r="B161" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>99</v>
+      </c>
+      <c r="B162" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>346</v>
+      </c>
+      <c r="B163" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>348</v>
+      </c>
+      <c r="B164" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>92</v>
+      </c>
+      <c r="B166" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B167" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>52</v>
+      </c>
+      <c r="B168" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>108</v>
+      </c>
+      <c r="B169" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>108</v>
+      </c>
+      <c r="B170" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>89</v>
+      </c>
+      <c r="B171" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>66</v>
+      </c>
+      <c r="B172" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>50</v>
+      </c>
+      <c r="B173" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>357</v>
+      </c>
+      <c r="B174" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>359</v>
+      </c>
+      <c r="B175" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>361</v>
+      </c>
+      <c r="B176" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>363</v>
+      </c>
+      <c r="B177" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="6"/>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="1"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B277" xr:uid="{4422D7C9-8DA6-4D05-8090-0A60A1B77BA5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B270">
+    <sortCondition ref="A2:A270"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04419A4-ABD5-463C-A44D-E18099D3F2F0}">
   <dimension ref="A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="20.7265625" customWidth="1"/>
+    <col min="1" max="1" width="20.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>5</v>
       </c>

--- a/исправления внести/слова2.xlsx
+++ b/исправления внести/слова2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33951B56-4C24-49D9-AF2F-180BE39066C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0648F560-A205-4988-B7D5-33A7EC2547A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19305" yWindow="3330" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView minimized="1" xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="8904" activeTab="2" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="cоставные" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="271">
   <si>
     <t>биологический структурализм</t>
   </si>
@@ -106,24 +106,12 @@
     <t>молекулярную устройства углерода</t>
   </si>
   <si>
-    <t>как "считывается" сведения</t>
-  </si>
-  <si>
-    <t>как "считываются" сведения</t>
-  </si>
-  <si>
     <t>внедрение энергоинформационного зараза</t>
   </si>
   <si>
     <t>внедрение энергоинформационной заразы</t>
   </si>
   <si>
-    <t>и эта зараза дал намеченые плоды</t>
-  </si>
-  <si>
-    <t>и эта зараза дала намеченые плоды</t>
-  </si>
-  <si>
     <t>любые сведения из Несущих сведения Полей должна восприниматься</t>
   </si>
   <si>
@@ -160,12 +148,6 @@
     <t>время изменения позволило выявить следующее</t>
   </si>
   <si>
-    <t>к снижению  энергетической возможности человека</t>
-  </si>
-  <si>
-    <t>к снижению  энергетического возможности человека</t>
-  </si>
-  <si>
     <t>рядом количественного скачка</t>
   </si>
   <si>
@@ -196,27 +178,15 @@
     <t>перевод</t>
   </si>
   <si>
-    <t>энергоинформационный</t>
-  </si>
-  <si>
     <t>фаллос</t>
   </si>
   <si>
-    <t>энвальтирование</t>
-  </si>
-  <si>
-    <t>эгрэгор</t>
-  </si>
-  <si>
     <t>эксирополяция</t>
   </si>
   <si>
     <t>микролептонных</t>
   </si>
   <si>
-    <t>тахионных</t>
-  </si>
-  <si>
     <t>животно</t>
   </si>
   <si>
@@ -229,9 +199,6 @@
     <t xml:space="preserve">аквариумист </t>
   </si>
   <si>
-    <t>станции</t>
-  </si>
-  <si>
     <t xml:space="preserve">Морфогенным </t>
   </si>
   <si>
@@ -244,48 +211,24 @@
     <t>органов</t>
   </si>
   <si>
-    <t xml:space="preserve">энергетической </t>
-  </si>
-  <si>
-    <t xml:space="preserve">жестикулирующий </t>
-  </si>
-  <si>
-    <t>биоэнергетик</t>
-  </si>
-  <si>
     <t>кампании</t>
   </si>
   <si>
-    <t xml:space="preserve">антимиры </t>
-  </si>
-  <si>
     <t>робот</t>
   </si>
   <si>
     <t xml:space="preserve">космологический </t>
   </si>
   <si>
-    <t xml:space="preserve">иммунную </t>
-  </si>
-  <si>
     <t xml:space="preserve">голографическую </t>
   </si>
   <si>
     <t xml:space="preserve">метакодом </t>
   </si>
   <si>
-    <t xml:space="preserve">инвалидов </t>
-  </si>
-  <si>
-    <t xml:space="preserve">биополевой </t>
-  </si>
-  <si>
     <t xml:space="preserve">кодированная </t>
   </si>
   <si>
-    <t xml:space="preserve">Биоэнергетические </t>
-  </si>
-  <si>
     <t>нуклиды</t>
   </si>
   <si>
@@ -295,18 +238,6 @@
     <t xml:space="preserve">неперсонификации </t>
   </si>
   <si>
-    <t xml:space="preserve">нуклон </t>
-  </si>
-  <si>
-    <t>частица являющаяся основным составляющим атомного ядра</t>
-  </si>
-  <si>
-    <t>синапсов</t>
-  </si>
-  <si>
-    <t>место еонтактк между двумя нейронами</t>
-  </si>
-  <si>
     <t xml:space="preserve">биолокационными </t>
   </si>
   <si>
@@ -316,15 +247,6 @@
     <t>энергетики</t>
   </si>
   <si>
-    <t>аура</t>
-  </si>
-  <si>
-    <t>невидимая оболочка вокруг живых существ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">экологическая </t>
-  </si>
-  <si>
     <t xml:space="preserve">неоткорректированных </t>
   </si>
   <si>
@@ -343,12 +265,6 @@
     <t>тип лучистой энергии невидимый для глаза</t>
   </si>
   <si>
-    <t xml:space="preserve">Хромосомы </t>
-  </si>
-  <si>
-    <t>стрруктурный элемент клеточного ядра содержащая опрелененный набор генов</t>
-  </si>
-  <si>
     <t xml:space="preserve">ультразвука </t>
   </si>
   <si>
@@ -361,21 +277,9 @@
     <t>ваш индивидуаьный гороскоп рождения</t>
   </si>
   <si>
-    <t xml:space="preserve">мембраны </t>
-  </si>
-  <si>
-    <t>тонкая пленка обладающая избирательной проницаемостью</t>
-  </si>
-  <si>
     <t xml:space="preserve">романа </t>
   </si>
   <si>
-    <t>энвольтировать</t>
-  </si>
-  <si>
-    <t>изготовление куклы  образа человека с использованием его фотографий</t>
-  </si>
-  <si>
     <t>панспермии</t>
   </si>
   <si>
@@ -385,18 +289,6 @@
     <t>сериалу</t>
   </si>
   <si>
-    <t>телебоевиков</t>
-  </si>
-  <si>
-    <t>жанр фильма или телесериала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">агентство </t>
-  </si>
-  <si>
-    <t>компания организация</t>
-  </si>
-  <si>
     <t>аквариуме</t>
   </si>
   <si>
@@ -418,12 +310,6 @@
     <t>лорганические соединения белков</t>
   </si>
   <si>
-    <t>ангины</t>
-  </si>
-  <si>
-    <t>инфекционное заболевание миндалин</t>
-  </si>
-  <si>
     <t xml:space="preserve">астрофизические </t>
   </si>
   <si>
@@ -442,9 +328,6 @@
     <t>книга альбом карта</t>
   </si>
   <si>
-    <t xml:space="preserve"> свечение атмосфера биополе</t>
-  </si>
-  <si>
     <t>бактерий</t>
   </si>
   <si>
@@ -454,15 +337,6 @@
     <t>способность живых сущуств ощущать скрытые объекты</t>
   </si>
   <si>
-    <t>жизненное поле</t>
-  </si>
-  <si>
-    <t>целитель</t>
-  </si>
-  <si>
-    <t>целительные</t>
-  </si>
-  <si>
     <t xml:space="preserve">борону </t>
   </si>
   <si>
@@ -475,12 +349,6 @@
     <t>нарушитель охотничьих правил</t>
   </si>
   <si>
-    <t>бронхиты</t>
-  </si>
-  <si>
-    <t>воспаление бронхов</t>
-  </si>
-  <si>
     <t xml:space="preserve">варикозному </t>
   </si>
   <si>
@@ -511,18 +379,6 @@
     <t>разрушуние эритрицитов</t>
   </si>
   <si>
-    <t xml:space="preserve">геоцентрической </t>
-  </si>
-  <si>
-    <t>центрированный на Земле</t>
-  </si>
-  <si>
-    <t xml:space="preserve">гильотина </t>
-  </si>
-  <si>
-    <t>ножницы эшафот резак</t>
-  </si>
-  <si>
     <t>глюонного</t>
   </si>
   <si>
@@ -595,9 +451,6 @@
     <t>круг мельница</t>
   </si>
   <si>
-    <t>махающий руками</t>
-  </si>
-  <si>
     <t>низкий грубый</t>
   </si>
   <si>
@@ -607,30 +460,6 @@
     <t>уравнено согласовано составлено</t>
   </si>
   <si>
-    <t>икон</t>
-  </si>
-  <si>
-    <t>лицо образ изображение</t>
-  </si>
-  <si>
-    <t>защитную</t>
-  </si>
-  <si>
-    <t>калека  убогий</t>
-  </si>
-  <si>
-    <t>инквизиция</t>
-  </si>
-  <si>
-    <t>пытка мучение терзание</t>
-  </si>
-  <si>
-    <t xml:space="preserve">интернационалист </t>
-  </si>
-  <si>
-    <t>мирожитель гражданин мира</t>
-  </si>
-  <si>
     <t>тепловой термический</t>
   </si>
   <si>
@@ -640,21 +469,9 @@
     <t>осеребреный</t>
   </si>
   <si>
-    <t>кадилом</t>
-  </si>
-  <si>
-    <t>сосуд богородское  зелье</t>
-  </si>
-  <si>
     <t>период война  деятельность работа</t>
   </si>
   <si>
-    <t xml:space="preserve">кандидатский </t>
-  </si>
-  <si>
-    <t>ученый докторский научный</t>
-  </si>
-  <si>
     <t>зашифрованная закодированная</t>
   </si>
   <si>
@@ -694,15 +511,6 @@
     <t>богатырь воевода воин</t>
   </si>
   <si>
-    <t>перепонка покров</t>
-  </si>
-  <si>
-    <t xml:space="preserve">менталитете </t>
-  </si>
-  <si>
-    <t>ум мышление мировозрение</t>
-  </si>
-  <si>
     <t>система знаков</t>
   </si>
   <si>
@@ -748,9 +556,6 @@
     <t>излтопы радионуклиды</t>
   </si>
   <si>
-    <t>ядерная частица</t>
-  </si>
-  <si>
     <t xml:space="preserve">одномандатные </t>
   </si>
   <si>
@@ -814,12 +619,6 @@
     <t>откликнувшиеся отозвавшиеся</t>
   </si>
   <si>
-    <t>оформлением</t>
-  </si>
-  <si>
-    <t>документ  удостоверение</t>
-  </si>
-  <si>
     <t xml:space="preserve">офтальмологической </t>
   </si>
   <si>
@@ -928,12 +727,6 @@
     <t>экстремисты бунтари новаторы</t>
   </si>
   <si>
-    <t xml:space="preserve">расфасовываются </t>
-  </si>
-  <si>
-    <t>пакуются фасуются сортируются</t>
-  </si>
-  <si>
     <t>режим</t>
   </si>
   <si>
@@ -952,12 +745,6 @@
     <t>ерунда чушь  глупость</t>
   </si>
   <si>
-    <t>светофоре</t>
-  </si>
-  <si>
-    <t>регулировщик</t>
-  </si>
-  <si>
     <t>секс</t>
   </si>
   <si>
@@ -979,48 +766,18 @@
     <t>многочасовой фильм</t>
   </si>
   <si>
-    <t>связь соединение</t>
-  </si>
-  <si>
-    <t>сканирование</t>
-  </si>
-  <si>
-    <t>цифровое копирование</t>
-  </si>
-  <si>
     <t xml:space="preserve">спеццентрала </t>
   </si>
   <si>
     <t>спеццентр</t>
   </si>
   <si>
-    <t>вокзал терминал транспортный узел</t>
-  </si>
-  <si>
-    <t>субкультуры</t>
-  </si>
-  <si>
-    <t>молодежные движения  молодежные стили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">суррогатной </t>
-  </si>
-  <si>
-    <t>заместительной поддельной ненастоящей</t>
-  </si>
-  <si>
     <t xml:space="preserve">сутенеров </t>
   </si>
   <si>
     <t>альфонс жигало растовщик</t>
   </si>
   <si>
-    <t>сверхсветовых</t>
-  </si>
-  <si>
-    <t>боевик на экране</t>
-  </si>
-  <si>
     <t xml:space="preserve">техническом </t>
   </si>
   <si>
@@ -1042,24 +799,12 @@
     <t>олигомеры полимеры</t>
   </si>
   <si>
-    <t xml:space="preserve">тромбоцитов </t>
-  </si>
-  <si>
-    <t>кровяные клетки</t>
-  </si>
-  <si>
     <t>звуковые волны неслышимые человеком</t>
   </si>
   <si>
     <t>невидимый</t>
   </si>
   <si>
-    <t>факультета</t>
-  </si>
-  <si>
-    <t>институт курс академия</t>
-  </si>
-  <si>
     <t xml:space="preserve">фибраналитической </t>
   </si>
   <si>
@@ -1081,60 +826,18 @@
     <t>оперирование</t>
   </si>
   <si>
-    <t>генные носители</t>
-  </si>
-  <si>
-    <t xml:space="preserve">хулиганов </t>
-  </si>
-  <si>
-    <t>буйный задира баловник</t>
-  </si>
-  <si>
     <t>шантажа</t>
   </si>
   <si>
     <t>давление угроза запугивание</t>
   </si>
   <si>
-    <t>натуральная природная органическая</t>
-  </si>
-  <si>
     <t>оценка предсказание прогнозирование</t>
   </si>
   <si>
-    <t>кукольная магия</t>
-  </si>
-  <si>
-    <t>окутывать обертывать</t>
-  </si>
-  <si>
     <t>мощность сила активность</t>
   </si>
   <si>
-    <t>силовой активной динамичной</t>
-  </si>
-  <si>
-    <t>вибрационный  энергетический</t>
-  </si>
-  <si>
-    <t>энергопотенциала</t>
-  </si>
-  <si>
-    <t>энергетический ресурс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">энергоцентр </t>
-  </si>
-  <si>
-    <t>энергоблок электростанция</t>
-  </si>
-  <si>
-    <t xml:space="preserve">эритроцитов </t>
-  </si>
-  <si>
-    <t>красные клетки крови</t>
-  </si>
-  <si>
     <t xml:space="preserve">этилового </t>
   </si>
   <si>
@@ -1148,12 +851,6 @@
   </si>
   <si>
     <t>статуя памятник</t>
-  </si>
-  <si>
-    <t>сервисах</t>
-  </si>
-  <si>
-    <t>услугах системах приложениях</t>
   </si>
   <si>
     <t>кроссворд</t>
@@ -1591,10 +1288,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157B4C6A-53EA-4FB9-AB5B-06694B8739E0}">
   <dimension ref="A5:B33"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.84375" customWidth="1"/>
-    <col min="2" max="2" width="67.23046875" customWidth="1"/>
+    <col min="1" max="1" width="48.83984375" customWidth="1"/>
+    <col min="2" max="2" width="67.20703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:2">
@@ -1604,10 +1301,10 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1628,34 +1325,34 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1668,10 +1365,10 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1684,10 +1381,10 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1706,14 +1403,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>8</v>
@@ -1722,28 +1411,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1752,10 +1425,10 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1768,10 +1441,10 @@
     </row>
     <row r="31" spans="1:2" s="3" customFormat="1">
       <c r="A31" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1784,10 +1457,10 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1802,1387 +1475,962 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4422D7C9-8DA6-4D05-8090-0A60A1B77BA5}">
   <dimension ref="A1:B270"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="28.23046875" customWidth="1"/>
+    <col min="2" max="2" width="28.20703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>88</v>
+      </c>
+      <c r="B8" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="B25" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>155</v>
-      </c>
-      <c r="B28" t="s">
-        <v>156</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>177</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>178</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="B41" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>71</v>
+      </c>
+      <c r="B43" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="B44" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>185</v>
-      </c>
-      <c r="B47" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>187</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>144</v>
+      </c>
+      <c r="B49" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>147</v>
+      </c>
+      <c r="B51" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>269</v>
       </c>
       <c r="B52" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="B53" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="B54" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="B57" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>198</v>
-      </c>
-      <c r="B58" t="s">
-        <v>199</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="B59" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="B60" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B61" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>161</v>
+      </c>
+      <c r="B62" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>204</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="B64" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>208</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>209</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>370</v>
+        <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>371</v>
+        <v>166</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>210</v>
+        <v>167</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>212</v>
+        <v>61</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>214</v>
-      </c>
-      <c r="B70" t="s">
-        <v>215</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="B72" t="s">
-        <v>216</v>
+        <v>173</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="B73" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>75</v>
+      <c r="A74" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="B76" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="B77" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>366</v>
+        <v>183</v>
       </c>
       <c r="B78" t="s">
-        <v>367</v>
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="B79" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="B80" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="B81" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>227</v>
-      </c>
-      <c r="B82" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>191</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="B84" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B85" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="B86" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="B87" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="B88" t="s">
-        <v>84</v>
+        <v>199</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="B89" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>365</v>
+        <v>202</v>
+      </c>
+      <c r="B90" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="B91" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="B92" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="B93" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="7" t="s">
-        <v>241</v>
+      <c r="A94" t="s">
+        <v>210</v>
       </c>
       <c r="B94" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="B95" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
       <c r="B96" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="B97" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="B98" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="B99" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="B100" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="B101" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="B102" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>258</v>
-      </c>
-      <c r="B103" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="B104" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="B105" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="B106" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="B107" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="B108" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="B109" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="B110" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="B111" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="B112" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="B113" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="B114" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="B115" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>281</v>
-      </c>
-      <c r="B116" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="B117" t="s">
-        <v>284</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>285</v>
-      </c>
-      <c r="B118" t="s">
-        <v>286</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>287</v>
+        <v>73</v>
       </c>
       <c r="B119" t="s">
-        <v>288</v>
+        <v>74</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>289</v>
+        <v>73</v>
       </c>
       <c r="B120" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>291</v>
+        <v>69</v>
       </c>
       <c r="B121" t="s">
-        <v>292</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B122" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>294</v>
-      </c>
-      <c r="B123" t="s">
-        <v>295</v>
+        <v>44</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>296</v>
-      </c>
-      <c r="B124" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>71</v>
+        <v>254</v>
       </c>
       <c r="B125" t="s">
-        <v>298</v>
+        <v>255</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="B126" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="B127" t="s">
-        <v>301</v>
+        <v>259</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>302</v>
+        <v>260</v>
       </c>
       <c r="B128" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" t="s">
-        <v>304</v>
+      <c r="A129" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="B129" t="s">
-        <v>305</v>
+        <v>262</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>306</v>
+        <v>66</v>
       </c>
       <c r="B130" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>308</v>
+        <v>264</v>
       </c>
       <c r="B131" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" t="s">
-        <v>368</v>
-      </c>
-      <c r="B132" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" t="s">
-        <v>112</v>
-      </c>
-      <c r="B133" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" t="s">
-        <v>85</v>
-      </c>
-      <c r="B134" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" t="s">
-        <v>85</v>
-      </c>
-      <c r="B135" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" t="s">
-        <v>312</v>
-      </c>
-      <c r="B136" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" t="s">
-        <v>314</v>
-      </c>
-      <c r="B137" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" t="s">
-        <v>61</v>
-      </c>
-      <c r="B138" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" t="s">
-        <v>317</v>
-      </c>
-      <c r="B139" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" t="s">
-        <v>319</v>
-      </c>
-      <c r="B140" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" t="s">
-        <v>321</v>
-      </c>
-      <c r="B141" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" t="s">
-        <v>56</v>
-      </c>
-      <c r="B142" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" t="s">
-        <v>113</v>
-      </c>
-      <c r="B143" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" t="s">
-        <v>113</v>
-      </c>
-      <c r="B144" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" t="s">
-        <v>325</v>
-      </c>
-      <c r="B145" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" t="s">
-        <v>327</v>
-      </c>
-      <c r="B146" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" t="s">
-        <v>330</v>
-      </c>
-      <c r="B148" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" t="s">
-        <v>332</v>
-      </c>
-      <c r="B150" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" t="s">
-        <v>101</v>
-      </c>
-      <c r="B151" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" t="s">
-        <v>101</v>
-      </c>
-      <c r="B152" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" t="s">
-        <v>95</v>
-      </c>
-      <c r="B153" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" t="s">
-        <v>95</v>
-      </c>
-      <c r="B154" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" t="s">
-        <v>336</v>
-      </c>
-      <c r="B155" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" t="s">
-        <v>339</v>
-      </c>
-      <c r="B158" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" t="s">
-        <v>341</v>
-      </c>
-      <c r="B159" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" t="s">
-        <v>343</v>
-      </c>
-      <c r="B160" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" t="s">
-        <v>99</v>
-      </c>
-      <c r="B161" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" t="s">
-        <v>99</v>
-      </c>
-      <c r="B162" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" t="s">
-        <v>346</v>
-      </c>
-      <c r="B163" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" t="s">
-        <v>348</v>
-      </c>
-      <c r="B164" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" t="s">
-        <v>92</v>
-      </c>
-      <c r="B166" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B167" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" t="s">
-        <v>52</v>
-      </c>
-      <c r="B168" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" t="s">
-        <v>108</v>
-      </c>
-      <c r="B169" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" t="s">
-        <v>108</v>
-      </c>
-      <c r="B170" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" t="s">
-        <v>89</v>
-      </c>
-      <c r="B171" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" t="s">
-        <v>66</v>
-      </c>
-      <c r="B172" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" t="s">
-        <v>50</v>
-      </c>
-      <c r="B173" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" t="s">
-        <v>357</v>
-      </c>
-      <c r="B174" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" t="s">
-        <v>359</v>
-      </c>
-      <c r="B175" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" t="s">
-        <v>361</v>
-      </c>
-      <c r="B176" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" t="s">
-        <v>363</v>
-      </c>
-      <c r="B177" t="s">
-        <v>364</v>
+        <v>265</v>
       </c>
     </row>
     <row r="231" spans="1:1">
@@ -3203,9 +2451,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04419A4-ABD5-463C-A44D-E18099D3F2F0}">
   <dimension ref="A2"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.69140625" customWidth="1"/>
+    <col min="1" max="1" width="20.68359375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:1">

--- a/исправления внести/слова2.xlsx
+++ b/исправления внести/слова2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0648F560-A205-4988-B7D5-33A7EC2547A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F97628E-A2F4-4C93-A97F-890CAC3C13F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="8904" activeTab="2" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="cоставные" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="263">
   <si>
     <t>биологический структурализм</t>
   </si>
@@ -94,30 +94,12 @@
     <t>Животным это используется в брачных танцах</t>
   </si>
   <si>
-    <t>Вода является двухмерной отображением рычага</t>
-  </si>
-  <si>
-    <t>Вода является двухмерным отображением рычага</t>
-  </si>
-  <si>
     <t>молекулярное устройство углерода</t>
   </si>
   <si>
     <t>молекулярную устройства углерода</t>
   </si>
   <si>
-    <t>внедрение энергоинформационного зараза</t>
-  </si>
-  <si>
-    <t>внедрение энергоинформационной заразы</t>
-  </si>
-  <si>
-    <t>любые сведения из Несущих сведения Полей должна восприниматься</t>
-  </si>
-  <si>
-    <t>любые сведения из Несущих сведений Полей должны восприниматься</t>
-  </si>
-  <si>
     <t>При этом образуется количественная устройство напоминающая</t>
   </si>
   <si>
@@ -152,12 +134,6 @@
   </si>
   <si>
     <t>рядом количественный скачок</t>
-  </si>
-  <si>
-    <t>касается не только определенной эниологической применения</t>
-  </si>
-  <si>
-    <t>касается не только определенного эниологического применения</t>
   </si>
   <si>
     <t>замысел "подсунул" очередную проверочный случай</t>
@@ -1299,21 +1275,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-    </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
@@ -1325,34 +1288,34 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1365,10 +1328,10 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1381,10 +1344,10 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1411,40 +1374,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" t="s">
-        <v>37</v>
-      </c>
-    </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="3" customFormat="1">
       <c r="A31" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1457,10 +1404,10 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1483,954 +1430,954 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B52" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B57" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B59" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B60" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B61" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B64" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B68" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B69" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B71" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B72" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="7" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B74" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B75" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B76" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B77" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B78" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B79" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B83" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B84" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B87" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B88" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B89" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B90" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B91" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B92" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B93" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B94" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B95" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B96" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B97" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B98" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B99" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B101" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B102" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B104" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B105" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B106" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B108" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B109" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B110" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B111" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B112" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B114" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B117" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B119" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B120" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B122" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B125" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B126" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B127" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B128" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B129" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B130" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B131" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="231" spans="1:1">

--- a/исправления внести/слова2.xlsx
+++ b/исправления внести/слова2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F97628E-A2F4-4C93-A97F-890CAC3C13F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B43490-1911-4E99-A088-3D5F2CA8CC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="cоставные" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="239">
   <si>
     <t>биологический структурализм</t>
   </si>
@@ -55,45 +55,9 @@
     <t>прямых излучений</t>
   </si>
   <si>
-    <t>возможны два исхода его возврата</t>
-  </si>
-  <si>
-    <t>возможны два исхода ее возврата</t>
-  </si>
-  <si>
     <t>контактантов</t>
   </si>
   <si>
-    <t>запасенный жизненный щаряд вращение скрученного</t>
-  </si>
-  <si>
-    <t>запасенный жизненный заряд вращение скрученного</t>
-  </si>
-  <si>
-    <t>изменяющее спиновую положение неделимых частиц</t>
-  </si>
-  <si>
-    <t>изменяющее спиновое положение неделимых частиц</t>
-  </si>
-  <si>
-    <t>ДНК представляет собой двойную завиток</t>
-  </si>
-  <si>
-    <t>ДНК представляет собой двойной завиток</t>
-  </si>
-  <si>
-    <t>Земля выгдядит количественный завитком напоминающей пружину</t>
-  </si>
-  <si>
-    <t>Земля выгдядит количественным завитком напоминающим пружину</t>
-  </si>
-  <si>
-    <t>Животно это используется в брачных танцах</t>
-  </si>
-  <si>
-    <t>Животным это используется в брачных танцах</t>
-  </si>
-  <si>
     <t>молекулярное устройство углерода</t>
   </si>
   <si>
@@ -106,46 +70,10 @@
     <t>При этом образуется количественное  устройство напоминаящее</t>
   </si>
   <si>
-    <t>выполлняют основную значение</t>
-  </si>
-  <si>
-    <t>выполлняют основное значение</t>
-  </si>
-  <si>
-    <t>есть какая то щелчка, действующая на погибель</t>
-  </si>
-  <si>
-    <t>есть какой то щелчок, действующий на погибель</t>
-  </si>
-  <si>
-    <t>два года назад могла за считанные минуты пройти</t>
-  </si>
-  <si>
-    <t>два года назад могло за считанные минуты пройти</t>
-  </si>
-  <si>
-    <t>время изменения позволил выявить следующее</t>
-  </si>
-  <si>
-    <t>время изменения позволило выявить следующее</t>
-  </si>
-  <si>
     <t>рядом количественного скачка</t>
   </si>
   <si>
     <t>рядом количественный скачок</t>
-  </si>
-  <si>
-    <t>замысел "подсунул" очередную проверочный случай</t>
-  </si>
-  <si>
-    <t>замысел "подсунул" очередной проверочный случай</t>
-  </si>
-  <si>
-    <t>выглядел ход энергоинформационной изменения</t>
-  </si>
-  <si>
-    <t>выглядел ход энергоинформационного изменения</t>
   </si>
   <si>
     <t>исходные</t>
@@ -1270,109 +1198,13 @@
     <col min="2" max="2" width="67.20703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:1">
       <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1"/>
@@ -1380,18 +1212,18 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="3" customFormat="1">
       <c r="A31" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1404,10 +1236,10 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1430,954 +1262,954 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B51" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="B52" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="B60" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B65" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="7" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B81" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="B83" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="B84" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B87" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B92" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="B94" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="B95" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="B96" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="B97" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="B98" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="B99" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="B100" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B101" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="B104" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B105" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B107" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="B108" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B109" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="B110" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B111" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="B112" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B113" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="B114" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="B115" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="B117" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B119" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B120" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B121" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B122" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="B125" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="B126" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="B127" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="B128" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B130" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="B131" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
     </row>
     <row r="231" spans="1:1">
@@ -2405,7 +2237,7 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/слова2.xlsx
+++ b/исправления внести/слова2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B43490-1911-4E99-A088-3D5F2CA8CC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20526B3E-BDF8-478A-B1C4-BCF154B6366F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" activeTab="1" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{A36FE745-F63C-475F-9E4A-28110238F7D2}"/>
   </bookViews>
   <sheets>
     <sheet name="cоставные" sheetId="2" r:id="rId1"/>
